--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DECPROCON CAROLINAS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DECPROCON CAROLINAS.xlsx
@@ -565,13 +565,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>19.2217</v>
+        <v>10.7194</v>
       </c>
       <c r="E2" t="n">
-        <v>8.168900000000001</v>
+        <v>2.4436</v>
       </c>
       <c r="F2" t="n">
-        <v>11.0531</v>
+        <v>8.275700000000001</v>
       </c>
       <c r="G2" t="n">
         <v>-0.7051999999999994</v>
@@ -610,13 +610,13 @@
         <v>32.6451</v>
       </c>
       <c r="S2" t="n">
-        <v>12.4994</v>
+        <v>3.997</v>
       </c>
       <c r="T2" t="n">
-        <v>6.715999999999999</v>
+        <v>0.991</v>
       </c>
       <c r="U2" t="n">
-        <v>5.783200000000001</v>
+        <v>3.0059</v>
       </c>
       <c r="V2" t="n">
         <v>-5.2155</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2852</v>
+        <v>0.5594</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0213</v>
+        <v>0.2161</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2639</v>
+        <v>0.3433</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7279</v>
@@ -766,13 +766,13 @@
         <v>0.5661</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1946</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0465</v>
+        <v>0.1484</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1481</v>
+        <v>-0.0688</v>
       </c>
       <c r="V4" t="n">
         <v>0.6415999999999999</v>
@@ -799,13 +799,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.8204</v>
+        <v>-3.5128</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.8204</v>
+        <v>-1.8831</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0002</v>
+        <v>-1.6298</v>
       </c>
       <c r="G5" t="n">
         <v>-4.7808</v>
@@ -844,13 +844,13 @@
         <v>2.0757</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6248</v>
+        <v>-0.3172</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7243999999999999</v>
+        <v>0.2131</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9005000000000001</v>
+        <v>-0.5302</v>
       </c>
       <c r="V5" t="n">
         <v>0.6415999999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>-11.657</v>
+        <v>-8.710599999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6182</v>
+        <v>-20.1375</v>
       </c>
       <c r="F6" t="n">
-        <v>-16.2753</v>
+        <v>11.4267</v>
       </c>
       <c r="G6" t="n">
-        <v>-18.7822</v>
+        <v>-0.6963999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-9.639099999999999</v>
+        <v>1.2093</v>
       </c>
       <c r="I6" t="n">
-        <v>-9.142900000000001</v>
+        <v>-1.9054</v>
       </c>
       <c r="J6" t="n">
-        <v>5.0176</v>
+        <v>18.7342</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3581</v>
+        <v>15.8399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6597999999999998</v>
+        <v>2.8939</v>
       </c>
       <c r="M6" t="n">
-        <v>-23.7995</v>
+        <v>-19.4302</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.9972</v>
+        <v>-14.6309</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.8025</v>
+        <v>-4.7995</v>
       </c>
       <c r="P6" t="n">
-        <v>8.680199999999999</v>
+        <v>-1.509599999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-18.1152</v>
+        <v>-52.4586</v>
       </c>
       <c r="R6" t="n">
-        <v>26.7954</v>
+        <v>50.949</v>
       </c>
       <c r="S6" t="n">
-        <v>12.1876</v>
+        <v>-7.7083</v>
       </c>
       <c r="T6" t="n">
-        <v>11.3777</v>
+        <v>-7.5414</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8099</v>
+        <v>-0.1667999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-13.7427</v>
+        <v>1.203300000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>6.338</v>
+        <v>21.1284</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.0806</v>
+        <v>-19.925</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. FUENTES GOMEZ</t>
+          <t>O. KOVAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>-11.9289</v>
+        <v>-11.3212</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5884</v>
+        <v>-7.0319</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.340400000000001</v>
+        <v>-4.289400000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.7238</v>
+        <v>-10.991</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.8323</v>
+        <v>-4.5225</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8918</v>
+        <v>-6.4685</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1283999999999996</v>
+        <v>-4.6252</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2264000000000002</v>
+        <v>-1.641</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3544999999999999</v>
+        <v>-2.9839</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.8522</v>
+        <v>-6.366</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.606</v>
+        <v>-2.8816</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.2463</v>
+        <v>-3.4846</v>
       </c>
       <c r="P7" t="n">
-        <v>3.5853</v>
+        <v>5.094900000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.6418</v>
+        <v>-3.2079</v>
       </c>
       <c r="R7" t="n">
-        <v>6.2271</v>
+        <v>8.302800000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.6778</v>
+        <v>-3.8367</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.075</v>
+        <v>-1.6513</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6029</v>
+        <v>-2.1853</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.1124</v>
+        <v>-1.5884</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4524</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.1124</v>
+        <v>-4.0408</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. KOVAL</t>
+          <t>L. FUENTES GOMEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>-12.583</v>
+        <v>-12.0465</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.714</v>
+        <v>-4.971</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.8691</v>
+        <v>-7.0753</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.991</v>
+        <v>-5.7238</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.5225</v>
+        <v>-2.8323</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.4685</v>
+        <v>-2.8918</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.6252</v>
+        <v>0.1283999999999996</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.641</v>
+        <v>-0.2264000000000002</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.9839</v>
+        <v>0.3544999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.366</v>
+        <v>-5.8522</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.8816</v>
+        <v>-2.606</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.4846</v>
+        <v>-3.2463</v>
       </c>
       <c r="P8" t="n">
-        <v>5.094900000000001</v>
+        <v>3.5853</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.2079</v>
+        <v>-2.6418</v>
       </c>
       <c r="R8" t="n">
-        <v>8.302800000000001</v>
+        <v>6.2271</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.0985</v>
+        <v>-2.7954</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.3333</v>
+        <v>-2.4575</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.7652</v>
+        <v>-0.3378</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5884</v>
+        <v>-7.1124</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4524</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.0408</v>
+        <v>-7.1124</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>J. MARTINEZ MUNOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.3254</v>
+        <v>-14.7456</v>
       </c>
       <c r="E9" t="n">
-        <v>-19.7231</v>
+        <v>-15.4554</v>
       </c>
       <c r="F9" t="n">
-        <v>5.398</v>
+        <v>0.7100000000000004</v>
       </c>
       <c r="G9" t="n">
-        <v>-24.1219</v>
+        <v>-15.3372</v>
       </c>
       <c r="H9" t="n">
-        <v>-25.16</v>
+        <v>-10.3265</v>
       </c>
       <c r="I9" t="n">
-        <v>1.037799999999999</v>
+        <v>-5.0109</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.8542</v>
+        <v>-6.7384</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.7873</v>
+        <v>-4.9501</v>
       </c>
       <c r="L9" t="n">
-        <v>3.9331</v>
+        <v>-1.7882</v>
       </c>
       <c r="M9" t="n">
-        <v>-16.2675</v>
+        <v>-8.5989</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.3729</v>
+        <v>-5.3761</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.894900000000001</v>
+        <v>-3.2225</v>
       </c>
       <c r="P9" t="n">
-        <v>15.8508</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q9" t="n">
-        <v>-25.4745</v>
+        <v>-16.983</v>
       </c>
       <c r="R9" t="n">
-        <v>41.3253</v>
+        <v>15.4734</v>
       </c>
       <c r="S9" t="n">
-        <v>6.1669</v>
+        <v>-3.2499</v>
       </c>
       <c r="T9" t="n">
-        <v>5.021800000000001</v>
+        <v>-1.9407</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1447</v>
+        <v>-1.3093</v>
       </c>
       <c r="V9" t="n">
-        <v>-12.2211</v>
+        <v>5.3509</v>
       </c>
       <c r="W9" t="n">
-        <v>8.583400000000001</v>
+        <v>10.2064</v>
       </c>
       <c r="X9" t="n">
-        <v>-20.8046</v>
+        <v>-4.8555</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NAVARRO MORALES</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>-17.8729</v>
+        <v>-15.1144</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.4887</v>
+        <v>-20.5554</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.384399999999999</v>
+        <v>5.441000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.440900000000001</v>
+        <v>-15.1965</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.4771</v>
+        <v>-4.5102</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0363</v>
+        <v>-10.6863</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3486</v>
+        <v>13.9689</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7863</v>
+        <v>12.8865</v>
       </c>
       <c r="L10" t="n">
-        <v>3.1345</v>
+        <v>1.0827</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.789099999999999</v>
+        <v>-29.1654</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.6909</v>
+        <v>-17.3965</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0984</v>
+        <v>-11.7689</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.9627</v>
+        <v>11.322</v>
       </c>
       <c r="Q10" t="n">
-        <v>-16.6056</v>
+        <v>-44.9106</v>
       </c>
       <c r="R10" t="n">
-        <v>12.6429</v>
+        <v>56.2326</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3421</v>
+        <v>-6.4024</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8157999999999999</v>
+        <v>-7.686500000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5263</v>
+        <v>1.2843</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.1273</v>
+        <v>-4.8377</v>
       </c>
       <c r="W10" t="n">
-        <v>5.5844</v>
+        <v>18.0723</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.7117</v>
+        <v>-22.9101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>J. NAVARRO MORALES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.8439</v>
+        <v>-15.6113</v>
       </c>
       <c r="E11" t="n">
-        <v>-26.1094</v>
+        <v>-9.2758</v>
       </c>
       <c r="F11" t="n">
-        <v>7.2653</v>
+        <v>-6.3353</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6963999999999999</v>
+        <v>-7.440900000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2093</v>
+        <v>-8.4771</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9054</v>
+        <v>1.0363</v>
       </c>
       <c r="J11" t="n">
-        <v>18.7342</v>
+        <v>1.3486</v>
       </c>
       <c r="K11" t="n">
-        <v>15.8399</v>
+        <v>-1.7863</v>
       </c>
       <c r="L11" t="n">
-        <v>2.8939</v>
+        <v>3.1345</v>
       </c>
       <c r="M11" t="n">
-        <v>-19.4302</v>
+        <v>-8.789099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-14.6309</v>
+        <v>-6.6909</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.7995</v>
+        <v>-2.0984</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.509599999999999</v>
+        <v>-3.9627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-52.4586</v>
+        <v>-16.6056</v>
       </c>
       <c r="R11" t="n">
-        <v>50.949</v>
+        <v>12.6429</v>
       </c>
       <c r="S11" t="n">
-        <v>-17.8414</v>
+        <v>-0.08049999999999996</v>
       </c>
       <c r="T11" t="n">
-        <v>-13.5134</v>
+        <v>0.3968</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.3281</v>
+        <v>-0.4774000000000002</v>
       </c>
       <c r="V11" t="n">
-        <v>1.203300000000001</v>
+        <v>-4.1273</v>
       </c>
       <c r="W11" t="n">
-        <v>21.1284</v>
+        <v>5.5844</v>
       </c>
       <c r="X11" t="n">
-        <v>-19.925</v>
+        <v>-9.7117</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.2779</v>
+        <v>-16.2741</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.9992</v>
+        <v>-11.205</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.278799999999999</v>
+        <v>-5.0689</v>
       </c>
       <c r="G12" t="n">
         <v>-5.6632</v>
@@ -1390,13 +1390,13 @@
         <v>7.3593</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.8116</v>
+        <v>-1.8076</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.0877</v>
+        <v>-2.2933</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7243000000000001</v>
+        <v>0.4859</v>
       </c>
       <c r="V12" t="n">
         <v>-7.6709</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.1642</v>
+        <v>-21.06</v>
       </c>
       <c r="E13" t="n">
-        <v>-22.7641</v>
+        <v>-26.2062</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6004</v>
+        <v>5.1462</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.1965</v>
+        <v>-24.1219</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.5102</v>
+        <v>-25.16</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.6863</v>
+        <v>1.037799999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>13.9689</v>
+        <v>-7.8542</v>
       </c>
       <c r="K13" t="n">
-        <v>12.8865</v>
+        <v>-11.7873</v>
       </c>
       <c r="L13" t="n">
-        <v>1.0827</v>
+        <v>3.9331</v>
       </c>
       <c r="M13" t="n">
-        <v>-29.1654</v>
+        <v>-16.2675</v>
       </c>
       <c r="N13" t="n">
-        <v>-17.3965</v>
+        <v>-13.3729</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.7689</v>
+        <v>-2.894900000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>11.322</v>
+        <v>15.8508</v>
       </c>
       <c r="Q13" t="n">
-        <v>-44.9106</v>
+        <v>-25.4745</v>
       </c>
       <c r="R13" t="n">
-        <v>56.2326</v>
+        <v>41.3253</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.4521</v>
+        <v>-0.5677999999999997</v>
       </c>
       <c r="T13" t="n">
-        <v>-9.8955</v>
+        <v>-1.4608</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5565</v>
+        <v>0.8931</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.8377</v>
+        <v>-12.2211</v>
       </c>
       <c r="W13" t="n">
-        <v>18.0723</v>
+        <v>8.583400000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-22.9101</v>
+        <v>-20.8046</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MUNOZ</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.5893</v>
+        <v>-21.0606</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.0382</v>
+        <v>-4.7306</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5511</v>
+        <v>-16.3296</v>
       </c>
       <c r="G14" t="n">
-        <v>-15.3372</v>
+        <v>-18.7822</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.3265</v>
+        <v>-9.639099999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.0109</v>
+        <v>-9.142900000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.7384</v>
+        <v>5.0176</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.9501</v>
+        <v>4.3581</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.7882</v>
+        <v>0.6597999999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.5989</v>
+        <v>-23.7995</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.3761</v>
+        <v>-13.9972</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.2225</v>
+        <v>-9.8025</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5096</v>
+        <v>8.680199999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.983</v>
+        <v>-18.1152</v>
       </c>
       <c r="R14" t="n">
-        <v>15.4734</v>
+        <v>26.7954</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.0934</v>
+        <v>2.7843</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.5234</v>
+        <v>2.0288</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5702</v>
+        <v>0.7551000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>5.3509</v>
+        <v>-13.7427</v>
       </c>
       <c r="W14" t="n">
-        <v>10.2064</v>
+        <v>6.338</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.8555</v>
+        <v>-20.0806</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.3944</v>
+        <v>-24.5189</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.5612</v>
+        <v>-13.4204</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.8334</v>
+        <v>-11.0984</v>
       </c>
       <c r="G15" t="n">
         <v>-23.9794</v>
@@ -1624,13 +1624,13 @@
         <v>28.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.0257</v>
+        <v>-4.1498</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9533</v>
+        <v>-1.9057</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.979</v>
+        <v>-2.2442</v>
       </c>
       <c r="V15" t="n">
         <v>-14.5047</v>
@@ -1657,13 +1657,13 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-38.3853</v>
+        <v>-29.5089</v>
       </c>
       <c r="E16" t="n">
-        <v>-53.9563</v>
+        <v>-45.2009</v>
       </c>
       <c r="F16" t="n">
-        <v>15.5709</v>
+        <v>15.6919</v>
       </c>
       <c r="G16" t="n">
         <v>-29.6526</v>
@@ -1702,13 +1702,13 @@
         <v>45.0993</v>
       </c>
       <c r="S16" t="n">
-        <v>-14.5779</v>
+        <v>-5.7014</v>
       </c>
       <c r="T16" t="n">
-        <v>-16.0272</v>
+        <v>-7.2719</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4494</v>
+        <v>1.5701</v>
       </c>
       <c r="V16" t="n">
         <v>17.5442</v>
@@ -1735,13 +1735,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>-43.4884</v>
+        <v>-35.317</v>
       </c>
       <c r="E17" t="n">
-        <v>-37.603</v>
+        <v>-32.6305</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.8853</v>
+        <v>-2.6865</v>
       </c>
       <c r="G17" t="n">
         <v>-13.7268</v>
@@ -1780,13 +1780,13 @@
         <v>35.853</v>
       </c>
       <c r="S17" t="n">
-        <v>-16.8308</v>
+        <v>-8.659599999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-10.3593</v>
+        <v>-5.3866</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.472</v>
+        <v>-3.2727</v>
       </c>
       <c r="V17" t="n">
         <v>-15.3844</v>
@@ -1813,13 +1813,13 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>-51.9937</v>
+        <v>-44.6433</v>
       </c>
       <c r="E18" t="n">
-        <v>-36.6572</v>
+        <v>-30.7071</v>
       </c>
       <c r="F18" t="n">
-        <v>-15.3365</v>
+        <v>-13.9363</v>
       </c>
       <c r="G18" t="n">
         <v>-22.8208</v>
@@ -1858,13 +1858,13 @@
         <v>35.853</v>
       </c>
       <c r="S18" t="n">
-        <v>-15.2208</v>
+        <v>-7.8705</v>
       </c>
       <c r="T18" t="n">
-        <v>-11.8659</v>
+        <v>-5.9158</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.3549</v>
+        <v>-1.9547</v>
       </c>
       <c r="V18" t="n">
         <v>-18.6695</v>
@@ -1891,13 +1891,13 @@
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-287.7481</v>
+        <v>-258.0967</v>
       </c>
       <c r="E19" t="n">
-        <v>-248.1451</v>
+        <v>-236.6814</v>
       </c>
       <c r="F19" t="n">
-        <v>-39.60290000000001</v>
+        <v>-21.4147</v>
       </c>
       <c r="G19" t="n">
         <v>-196.2769</v>
@@ -1927,7 +1927,7 @@
         <v>-76.7936</v>
       </c>
       <c r="P19" t="n">
-        <v>64.15799999999999</v>
+        <v>64.158</v>
       </c>
       <c r="Q19" t="n">
         <v>-341.547</v>
@@ -1936,16 +1936,16 @@
         <v>405.705</v>
       </c>
       <c r="S19" t="n">
-        <v>-75.9376</v>
+        <v>-46.2861</v>
       </c>
       <c r="T19" t="n">
-        <v>-53.1986</v>
+        <v>-41.7334</v>
       </c>
       <c r="U19" t="n">
-        <v>-22.7408</v>
+        <v>-4.552799999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-79.693</v>
+        <v>-79.69300000000001</v>
       </c>
       <c r="W19" t="n">
         <v>127.0716</v>
